--- a/artfynd/A 17180-2024 artfynd.xlsx
+++ b/artfynd/A 17180-2024 artfynd.xlsx
@@ -2904,7 +2904,7 @@
         <v>126810187</v>
       </c>
       <c r="B20" t="n">
-        <v>99680</v>
+        <v>99683</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 17180-2024 artfynd.xlsx
+++ b/artfynd/A 17180-2024 artfynd.xlsx
@@ -2904,7 +2904,7 @@
         <v>126810187</v>
       </c>
       <c r="B20" t="n">
-        <v>99683</v>
+        <v>99684</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 17180-2024 artfynd.xlsx
+++ b/artfynd/A 17180-2024 artfynd.xlsx
@@ -2904,7 +2904,7 @@
         <v>126810187</v>
       </c>
       <c r="B20" t="n">
-        <v>99684</v>
+        <v>99689</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 17180-2024 artfynd.xlsx
+++ b/artfynd/A 17180-2024 artfynd.xlsx
@@ -2904,7 +2904,7 @@
         <v>126810187</v>
       </c>
       <c r="B20" t="n">
-        <v>99689</v>
+        <v>99691</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 17180-2024 artfynd.xlsx
+++ b/artfynd/A 17180-2024 artfynd.xlsx
@@ -2904,7 +2904,7 @@
         <v>126810187</v>
       </c>
       <c r="B20" t="n">
-        <v>99691</v>
+        <v>99697</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 17180-2024 artfynd.xlsx
+++ b/artfynd/A 17180-2024 artfynd.xlsx
@@ -2904,7 +2904,7 @@
         <v>126810187</v>
       </c>
       <c r="B20" t="n">
-        <v>99697</v>
+        <v>99699</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 17180-2024 artfynd.xlsx
+++ b/artfynd/A 17180-2024 artfynd.xlsx
@@ -2904,7 +2904,7 @@
         <v>126810187</v>
       </c>
       <c r="B20" t="n">
-        <v>99699</v>
+        <v>99700</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
